--- a/questionnaire_templates/022_skincare_routine_finder_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/022_skincare_routine_finder_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -823,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>recommended_products</t>
+          <t>recommended_products_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Recommended products</t>
+          <t>Recommended Products 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>recommended_products</t>
+          <t>recommended_products_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Recommended products</t>
+          <t>Recommended Products 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>product_formulations</t>
+          <t>product_formulations_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Product formulations</t>
+          <t>Product Formulations 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>product_formulations</t>
+          <t>product_formulations_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product formulations</t>
+          <t>Product Formulations 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>recommended_products</t>
+          <t>recommended_products_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Recommended products</t>
+          <t>Recommended Products 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>recommended_products</t>
+          <t>recommended_products_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Recommended products</t>
+          <t>Recommended Products 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -2388,83 +2388,66 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>product_formulations_choices</t>
+          <t>product_formulations_2_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>serum</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>serum</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>product_formulations_choices</t>
+          <t>product_formulations_2_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>product_formulations_choices</t>
+          <t>product_formulations_3_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>product_formulations_choices</t>
+          <t>product_formulations_3_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>product_formulations_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
         <is>
           <t>No</t>
         </is>
